--- a/example_files/example_inputs.xlsx
+++ b/example_files/example_inputs.xlsx
@@ -1,107 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ksrsa-my.sharepoint.com/personal/tomas_moreira_retail-consult_com/Documents/RC_DOCS/eureka/example_files/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_46EC2EEB8B9CD5306D88AFD726324A54C9876C7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52B80434-84D5-4EAE-ADF1-44BAA41D1D8F}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Input Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Real Data" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
-  <si>
-    <t>Segment_ID</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Packaging</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Temperature_C</t>
-  </si>
-  <si>
-    <t>Humidity_Percent</t>
-  </si>
-  <si>
-    <t>Ethylene_ppm</t>
-  </si>
-  <si>
-    <t>PT-LVT</t>
-  </si>
-  <si>
-    <t>Caixa de Cartão Aberta</t>
-  </si>
-  <si>
-    <t>2026-07-29</t>
-  </si>
-  <si>
-    <t>2026-07-30</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>PT-CL</t>
-  </si>
-  <si>
-    <t>Caixa de Plástico</t>
-  </si>
-  <si>
-    <t>2026-08-01</t>
-  </si>
-  <si>
-    <t>2026-08-02</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Real_BRIX</t>
-  </si>
-  <si>
-    <t>Real_Acidity</t>
-  </si>
-  <si>
-    <t>Real_Firmness</t>
-  </si>
-  <si>
-    <t>Real_Quality</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -120,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -422,224 +408,258 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Segment_ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Temperature_C</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Humidity_Percent</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ethylene_ppm</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Real_Firmness</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Real_BRIX</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Real_Acidity</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Real_Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PT-LVT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+      <c r="F2" t="n">
+        <v>90</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>22.7</v>
-      </c>
-      <c r="F2">
-        <v>66</v>
-      </c>
-      <c r="G2">
-        <v>6.5000000000000002E-2</v>
-      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PT-LVT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>89</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <v>23.9</v>
-      </c>
-      <c r="F3">
-        <v>62.6</v>
-      </c>
-      <c r="G3">
-        <v>0.06</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PT-LVT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>90</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>58</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4">
-        <v>25</v>
-      </c>
-      <c r="F4">
-        <v>63.2</v>
-      </c>
-      <c r="G4">
-        <v>6.9000000000000006E-2</v>
-      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PT-LVT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>91</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PT-LVT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="F5">
+      <c r="F6" t="n">
         <v>90</v>
       </c>
-      <c r="G5">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>4.5</v>
-      </c>
-      <c r="F6">
-        <v>91</v>
-      </c>
-      <c r="G6">
-        <v>0.02</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>11.2</v>
-      </c>
-      <c r="C2">
-        <v>0.6</v>
-      </c>
-      <c r="D2">
-        <v>60</v>
-      </c>
-      <c r="E2">
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K6" t="n">
         <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>11.5</v>
-      </c>
-      <c r="C3">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D3">
-        <v>55</v>
-      </c>
-      <c r="E3">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>0.5</v>
-      </c>
-      <c r="D4">
-        <v>45</v>
-      </c>
-      <c r="E4">
-        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/example_files/example_inputs.xlsx
+++ b/example_files/example_inputs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,25 +449,20 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Ethylene_ppm</t>
+          <t>Real_Firmness</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Real_Firmness</t>
+          <t>Real_BRIX</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Real_BRIX</t>
+          <t>Real_Acidity</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
-        <is>
-          <t>Real_Acidity</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>Real_Quality</t>
         </is>
@@ -499,18 +494,15 @@
         <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -539,13 +531,10 @@
       <c r="F3" t="n">
         <v>89</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -573,18 +562,15 @@
         <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1</v>
+        <v>58</v>
       </c>
       <c r="H4" t="n">
-        <v>58</v>
+        <v>10.2</v>
       </c>
       <c r="I4" t="n">
-        <v>10.2</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K4" t="n">
         <v>95</v>
       </c>
     </row>
@@ -613,13 +599,10 @@
       <c r="F5" t="n">
         <v>91</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -647,18 +630,15 @@
         <v>90</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
+        <v>55</v>
       </c>
       <c r="H6" t="n">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="I6" t="n">
-        <v>10.5</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K6" t="n">
         <v>90</v>
       </c>
     </row>

--- a/example_files/example_inputs.xlsx
+++ b/example_files/example_inputs.xlsx
@@ -1,34 +1,130 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pasta\eureka\example_files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D21C941-6130-4DB7-AB31-CF1E3981A8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Segment_ID</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Packaging</t>
+  </si>
+  <si>
+    <t>Temperature_C</t>
+  </si>
+  <si>
+    <t>Humidity_Percent</t>
+  </si>
+  <si>
+    <t>Real_Firmness</t>
+  </si>
+  <si>
+    <t>Real_BRIX</t>
+  </si>
+  <si>
+    <t>Real_Acidity</t>
+  </si>
+  <si>
+    <t>Real_Quality</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>PT-LVT</t>
+  </si>
+  <si>
+    <t>bulk</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>open_box</t>
+  </si>
+  <si>
+    <t>perforated_bag</t>
+  </si>
+  <si>
+    <t>map_sealed</t>
+  </si>
+  <si>
+    <t>PT-NI</t>
+  </si>
+  <si>
+    <t>PT-CL</t>
+  </si>
+  <si>
+    <t>PT-CI</t>
+  </si>
+  <si>
+    <t>PT-AL</t>
+  </si>
+  <si>
+    <t>PT-ALG</t>
+  </si>
+  <si>
+    <t>PT-SM</t>
+  </si>
+  <si>
+    <t>PT-MAD</t>
+  </si>
+  <si>
+    <t>PT-NL</t>
+  </si>
+  <si>
+    <t>PT-ACO</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +143,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,241 +445,226 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Segment_ID</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Packaging</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Temperature_C</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Humidity_Percent</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Real_Firmness</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Real_BRIX</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Real_Acidity</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Real_Quality</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PT-LVT</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
         <v>90</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>60</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>10</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="N2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PT-LVT</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3">
         <v>4.2</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>89</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="N3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PT-LVT</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F4">
         <v>90</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>58</v>
       </c>
-      <c r="H4" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="H4">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="I4">
         <v>0.9</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>95</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="N4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PT-LVT</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>91</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>PT-LVT</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>55</v>
+      </c>
+      <c r="H6">
+        <v>10.5</v>
+      </c>
+      <c r="I6">
+        <v>0.8</v>
+      </c>
+      <c r="J6">
         <v>90</v>
       </c>
-      <c r="G6" t="n">
-        <v>55</v>
-      </c>
-      <c r="H6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>90</v>
+      <c r="O6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O10" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D2:D6" xr:uid="{D941D888-5685-4440-888D-531C4E047AE3}">
+      <formula1>$N$1:$N$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="C2:C6" xr:uid="{3E864772-B17D-43F4-A129-971F2A65FB08}">
+      <formula1>$O$1:$O$10</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>